--- a/data/trans_dic/P64D$andando_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 22,63</t>
+          <t>9,05; 23,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,69; 63,5</t>
+          <t>42,43; 65,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,02; 36,44</t>
+          <t>23,0; 36,71</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,5; 22,77</t>
+          <t>9,59; 22,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,7; 37,2</t>
+          <t>25,42; 37,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 28,0</t>
+          <t>16,53; 27,81</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,74; 30,41</t>
+          <t>21,31; 30,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,49; 37,79</t>
+          <t>29,56; 37,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,37; 32,14</t>
+          <t>26,62; 32,27</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,21; 22,96</t>
+          <t>12,39; 22,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,72; 36,98</t>
+          <t>28,79; 37,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,27; 28,59</t>
+          <t>19,41; 28,45</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12713; 29898</t>
+          <t>11953; 30748</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33537; 51080</t>
+          <t>34136; 52604</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48927; 77462</t>
+          <t>48890; 78031</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>131373; 314824</t>
+          <t>132508; 312683</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>233407; 351504</t>
+          <t>240180; 353554</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>395133; 651562</t>
+          <t>384732; 647313</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97236; 136036</t>
+          <t>95323; 136533</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>128379; 164529</t>
+          <t>128708; 162735</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>232712; 283710</t>
+          <t>234972; 284806</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>259210; 450428</t>
+          <t>243140; 446693</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>419551; 540136</t>
+          <t>420586; 543253</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>693752; 978494</t>
+          <t>664389; 973570</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$andando_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,05; 23,28</t>
+          <t>11,19; 25,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,43; 65,39</t>
+          <t>38,42; 56,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 36,71</t>
+          <t>22,76; 34,03</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 22,62</t>
+          <t>19,73; 25,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,42; 37,41</t>
+          <t>34,46; 40,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,53; 27,81</t>
+          <t>26,76; 30,94</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,31; 30,53</t>
+          <t>21,78; 29,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,56; 37,38</t>
+          <t>29,6; 37,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,62; 32,27</t>
+          <t>26,7; 32,51</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 22,77</t>
+          <t>20,63; 25,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,79; 37,19</t>
+          <t>34,5; 38,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 28,45</t>
+          <t>27,35; 30,46</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19380</t>
+          <t>29128</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>41945</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61830</t>
+          <t>71073</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11953; 30748</t>
+          <t>18347; 41650</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34136; 52604</t>
+          <t>33811; 50096</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48890; 78031</t>
+          <t>57340; 85734</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>248484</t>
+          <t>283901</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311968</t>
+          <t>354963</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>560451</t>
+          <t>638864</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>132508; 312683</t>
+          <t>250696; 320960</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>240180; 353554</t>
+          <t>325756; 379450</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>384732; 647313</t>
+          <t>592947; 685539</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>114896</t>
+          <t>125037</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>143510</t>
+          <t>158021</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>258406</t>
+          <t>283059</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95323; 136533</t>
+          <t>106185; 145534</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>128708; 162735</t>
+          <t>141328; 177772</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>234972; 284806</t>
+          <t>257663; 313696</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>382759</t>
+          <t>438067</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>554929</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>880687</t>
+          <t>992996</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>243140; 446693</t>
+          <t>396492; 480445</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>420586; 543253</t>
+          <t>521134; 589002</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>664389; 973570</t>
+          <t>938885; 1045746</t>
         </is>
       </c>
     </row>
